--- a/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0003T0006Z000C1N35_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0003T0006Z000C1N35_analysis.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,10 +486,10 @@
         <v>10.94804390683442</v>
       </c>
       <c r="E2" t="n">
-        <v>4.19384506992207</v>
+        <v>4.040202352908559</v>
       </c>
       <c r="F2" t="n">
-        <v>4.149493967448629</v>
+        <v>3.982277929603225</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -518,10 +518,10 @@
         <v>6.623800406267105</v>
       </c>
       <c r="E3" t="n">
-        <v>4.19384506992207</v>
+        <v>4.040202352908559</v>
       </c>
       <c r="F3" t="n">
-        <v>4.149493967448629</v>
+        <v>3.982277929603225</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -550,10 +550,10 @@
         <v>17.75983684551525</v>
       </c>
       <c r="E4" t="n">
-        <v>4.19384506992207</v>
+        <v>4.040202352908559</v>
       </c>
       <c r="F4" t="n">
-        <v>4.149493967448629</v>
+        <v>3.982277929603225</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>17.49189835669215</v>
+        <v>8.894766027072855</v>
       </c>
       <c r="D5" t="n">
-        <v>15.26353845875414</v>
+        <v>8.331324308217106</v>
       </c>
       <c r="E5" t="n">
-        <v>4.19384506992207</v>
+        <v>4.040202352908559</v>
       </c>
       <c r="F5" t="n">
-        <v>4.149493967448629</v>
+        <v>3.982277929603225</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>5.169887873529034</v>
+        <v>17.49189835669215</v>
       </c>
       <c r="D6" t="n">
-        <v>7.552534124501075</v>
+        <v>15.26353845875414</v>
       </c>
       <c r="E6" t="n">
-        <v>4.19384506992207</v>
+        <v>4.040202352908559</v>
       </c>
       <c r="F6" t="n">
-        <v>4.149493967448629</v>
+        <v>3.982277929603225</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>13.92762302047277</v>
+        <v>5.169887873529034</v>
       </c>
       <c r="D7" t="n">
-        <v>12.76005750343527</v>
+        <v>7.552534124501075</v>
       </c>
       <c r="E7" t="n">
-        <v>4.19384506992207</v>
+        <v>4.040202352908559</v>
       </c>
       <c r="F7" t="n">
-        <v>4.149493967448629</v>
+        <v>3.982277929603225</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,23 +672,55 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
+        <v>13.92762302047277</v>
+      </c>
+      <c r="D8" t="n">
+        <v>12.76005750343527</v>
+      </c>
+      <c r="E8" t="n">
+        <v>4.040202352908559</v>
+      </c>
+      <c r="F8" t="n">
+        <v>3.982277929603225</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>T6165</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>G5</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>W0035F0003T0006Z000C1N35.png</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>8</v>
+      </c>
+      <c r="C9" t="n">
         <v>8.616058436530288</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D9" t="n">
         <v>6.254259420234907</v>
       </c>
-      <c r="E8" t="n">
-        <v>4.19384506992207</v>
-      </c>
-      <c r="F8" t="n">
-        <v>4.149493967448629</v>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="E9" t="n">
+        <v>4.040202352908559</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3.982277929603225</v>
+      </c>
+      <c r="G9" t="inlineStr">
         <is>
           <t>T6165</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>G5</t>
         </is>

--- a/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0003T0006Z000C1N35_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0003T0006Z000C1N35_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>11.90184233257415</v>
+        <v>1.934049379043299</v>
       </c>
       <c r="D2" t="n">
-        <v>10.94804390683442</v>
+        <v>1.779057134860593</v>
       </c>
       <c r="E2" t="n">
-        <v>4.040202352908559</v>
+        <v>0.656532882347641</v>
       </c>
       <c r="F2" t="n">
-        <v>3.982277929603225</v>
+        <v>0.6471201635605242</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>8.924730244802431</v>
+        <v>1.450268664780395</v>
       </c>
       <c r="D3" t="n">
-        <v>6.623800406267105</v>
+        <v>1.076367566018404</v>
       </c>
       <c r="E3" t="n">
-        <v>4.040202352908559</v>
+        <v>0.656532882347641</v>
       </c>
       <c r="F3" t="n">
-        <v>3.982277929603225</v>
+        <v>0.6471201635605242</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>16.68080619852488</v>
+        <v>2.710631007260294</v>
       </c>
       <c r="D4" t="n">
-        <v>17.75983684551525</v>
+        <v>2.885973487396227</v>
       </c>
       <c r="E4" t="n">
-        <v>4.040202352908559</v>
+        <v>0.656532882347641</v>
       </c>
       <c r="F4" t="n">
-        <v>3.982277929603225</v>
+        <v>0.6471201635605242</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>8.894766027072855</v>
+        <v>1.445399479399339</v>
       </c>
       <c r="D5" t="n">
-        <v>8.331324308217106</v>
+        <v>1.35384020008528</v>
       </c>
       <c r="E5" t="n">
-        <v>4.040202352908559</v>
+        <v>0.656532882347641</v>
       </c>
       <c r="F5" t="n">
-        <v>3.982277929603225</v>
+        <v>0.6471201635605242</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>17.49189835669215</v>
+        <v>2.842433482962474</v>
       </c>
       <c r="D6" t="n">
-        <v>15.26353845875414</v>
+        <v>2.480324999547548</v>
       </c>
       <c r="E6" t="n">
-        <v>4.040202352908559</v>
+        <v>0.656532882347641</v>
       </c>
       <c r="F6" t="n">
-        <v>3.982277929603225</v>
+        <v>0.6471201635605242</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>5.169887873529034</v>
+        <v>0.8401067794484681</v>
       </c>
       <c r="D7" t="n">
-        <v>7.552534124501075</v>
+        <v>1.227286795231425</v>
       </c>
       <c r="E7" t="n">
-        <v>4.040202352908559</v>
+        <v>0.656532882347641</v>
       </c>
       <c r="F7" t="n">
-        <v>3.982277929603225</v>
+        <v>0.6471201635605242</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>13.92762302047277</v>
+        <v>2.263238740826826</v>
       </c>
       <c r="D8" t="n">
-        <v>12.76005750343527</v>
+        <v>2.073509344308231</v>
       </c>
       <c r="E8" t="n">
-        <v>4.040202352908559</v>
+        <v>0.656532882347641</v>
       </c>
       <c r="F8" t="n">
-        <v>3.982277929603225</v>
+        <v>0.6471201635605242</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>8.616058436530288</v>
+        <v>1.400109495936172</v>
       </c>
       <c r="D9" t="n">
-        <v>6.254259420234907</v>
+        <v>1.016317155788172</v>
       </c>
       <c r="E9" t="n">
-        <v>4.040202352908559</v>
+        <v>0.656532882347641</v>
       </c>
       <c r="F9" t="n">
-        <v>3.982277929603225</v>
+        <v>0.6471201635605242</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
